--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:32:23+00:00</t>
+    <t>2026-09-16T15:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -759,7 +759,9 @@
   </si>
   <si>
     <t>Aussi utilisé pour indiquer qu'il n'y a pas d'acte ou qu'on ne sait pas s'il y en a.
-Si l'acte n'est pas trouvé dans CCAM, utiliser le code NCIT 'C25218' (Intervention)
+CCAM : terminologie facturante pour la production d'actes.
+SNOMED CT (additional binding) : terminologie pour la demande d'acte ou de report d'actes à des fins internationales, en cours de validation en Europe.
+Si l'acte n'est pas trouvé dans CCAM ni SNOMED CT, utiliser le code CISIS 'GEN-092.04.13' (Autre acte, additional binding)
 et décrire l'acte en texte libre dans la partie narrative.
 Pour les actes chirurgicaux inconnus, utiliser jdv-absent-or-unknown-procedure-cisis.</t>
   </si>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:06:55+00:00</t>
+    <t>2026-09-16T15:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:10:32+00:00</t>
+    <t>2026-09-16T15:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -752,7 +752,7 @@
 </t>
   </si>
   <si>
-    <t>Code d'acte</t>
+    <t>Code d'acte : CCAM (facturante), SNOMED CT (international, additional binding) ou CISIS 'Autre acte'/absent-unknown</t>
   </si>
   <si>
     <t>Identification of the procedure or recording of "absence of relevant procedures" or of "procedures unknown".</t>

--- a/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
+++ b/nr-doc-core-procedure/ig/StructureDefinition-fr-core-procedure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:30:48+00:00</t>
+    <t>2026-09-17T13:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
